--- a/Projects/Duncan-Robinson.xlsx
+++ b/Projects/Duncan-Robinson.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Documents/GitHub/basketball-analytics/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D3C4538-8B4F-B741-BE8A-F8CF02EB865F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4419ABC1-4048-AF4A-BAB7-80E56855AE2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" activeTab="11" xr2:uid="{91DDF0CC-1112-E742-B0ED-4CCF8B231B63}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" activeTab="5" xr2:uid="{91DDF0CC-1112-E742-B0ED-4CCF8B231B63}"/>
   </bookViews>
   <sheets>
     <sheet name="Per Game" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Per 36" sheetId="3" r:id="rId3"/>
     <sheet name="Per 100 Poss" sheetId="4" r:id="rId4"/>
     <sheet name="Advanced" sheetId="5" r:id="rId5"/>
-    <sheet name="Advanced Shooting" sheetId="6" r:id="rId6"/>
+    <sheet name="Adjusted Shooting" sheetId="6" r:id="rId6"/>
     <sheet name="Play-by-Play" sheetId="7" r:id="rId7"/>
     <sheet name="Shooting" sheetId="8" r:id="rId8"/>
     <sheet name="Game Highs" sheetId="10" r:id="rId9"/>
